--- a/static/dataset/bills_metadata.xlsx
+++ b/static/dataset/bills_metadata.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>Bill_id</t>
   </si>
@@ -66,14 +66,27 @@
   <si>
     <t>Passed</t>
   </si>
+  <si>
+    <t>Bill_003</t>
+  </si>
+  <si>
+    <t>One click file</t>
+  </si>
+  <si>
+    <t>Home affairs</t>
+  </si>
+  <si>
+    <t>Not Passed</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="d-mmm-yyyy"/>
     <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="166" formatCode="dd-mm-yyyy"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -106,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -120,6 +133,9 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -399,6 +415,26 @@
         <v>15</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="5">
+        <v>46023.0</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="B2"/>

--- a/static/dataset/bills_metadata.xlsx
+++ b/static/dataset/bills_metadata.xlsx
@@ -22,7 +22,7 @@
     <t>Intro_date</t>
   </si>
   <si>
-    <t>Ministry</t>
+    <t>Category</t>
   </si>
   <si>
     <t>House</t>

--- a/static/dataset/bills_metadata.xlsx
+++ b/static/dataset/bills_metadata.xlsx
@@ -19,7 +19,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Intro_date</t>
+    <t>Date Introduced</t>
   </si>
   <si>
     <t>Category</t>
@@ -352,6 +352,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="2" max="2" width="63.5"/>
+    <col customWidth="1" min="3" max="3" width="15.88"/>
     <col customWidth="1" min="4" max="4" width="50.88"/>
   </cols>
   <sheetData>

--- a/static/dataset/bills_metadata.xlsx
+++ b/static/dataset/bills_metadata.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>Bill_id</t>
   </si>
@@ -31,31 +31,25 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Bill_101</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>The Viksit Bharat Shiksha Adhishthan Bill, 2025</t>
-    </r>
-  </si>
-  <si>
-    <t>Education</t>
+    <t>Bill 105</t>
+  </si>
+  <si>
+    <t>Vikisit Bharath, 2026</t>
+  </si>
+  <si>
+    <t>Defense</t>
   </si>
   <si>
     <t>Lok Sabha</t>
   </si>
   <si>
-    <t>Pending</t>
-  </si>
-  <si>
-    <t>Bill_102</t>
-  </si>
-  <si>
-    <t>Water (Prevention and Control of Pollution) Amendment Bill, 2024</t>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>Bill 202</t>
+  </si>
+  <si>
+    <t>UGC Amendment Bill, 2026</t>
   </si>
   <si>
     <t>Environment, Forest and Climate Change</t>
@@ -64,19 +58,16 @@
     <t>Rajya Sabha</t>
   </si>
   <si>
-    <t>Passed</t>
-  </si>
-  <si>
-    <t>Bill_103</t>
-  </si>
-  <si>
-    <t>One click file</t>
-  </si>
-  <si>
-    <t>Home affairs</t>
-  </si>
-  <si>
-    <t>Not Passed</t>
+    <t>Bill 303</t>
+  </si>
+  <si>
+    <t>Apple Vision Pro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Passed</t>
   </si>
 </sst>
 </file>
@@ -88,7 +79,7 @@
     <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
     <numFmt numFmtId="166" formatCode="dd-mm-yyyy"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -99,10 +90,6 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <color rgb="FF0000FF"/>
     </font>
   </fonts>
   <fills count="2">
@@ -126,7 +113,7 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -408,7 +395,7 @@
         <v>12</v>
       </c>
       <c r="C3" s="4">
-        <v>45327.0</v>
+        <v>45323.0</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>13</v>
@@ -417,33 +404,30 @@
         <v>14</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="C4" s="5">
         <v>46023.0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink r:id="rId1" ref="B2"/>
-  </hyperlinks>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>